--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_30-01-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_30-01-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="152">
   <si>
     <t>SKU</t>
   </si>
@@ -244,229 +244,232 @@
     <t>£45.75</t>
   </si>
   <si>
+    <t>Add to Enquiry</t>
+  </si>
+  <si>
+    <t>£22.16</t>
+  </si>
+  <si>
+    <t>£47.08</t>
+  </si>
+  <si>
+    <t>£41.25</t>
+  </si>
+  <si>
+    <t>£27.49</t>
+  </si>
+  <si>
+    <t>£14.38</t>
+  </si>
+  <si>
+    <t>£16.01</t>
+  </si>
+  <si>
+    <t>£10.15</t>
+  </si>
+  <si>
+    <t>£12.47</t>
+  </si>
+  <si>
+    <t>£14.62</t>
+  </si>
+  <si>
+    <t>£15.68</t>
+  </si>
+  <si>
+    <t>£19.71</t>
+  </si>
+  <si>
+    <t>£22.56</t>
+  </si>
+  <si>
+    <t>£23.59</t>
+  </si>
+  <si>
+    <t>£27.44</t>
+  </si>
+  <si>
+    <t>£27.15</t>
+  </si>
+  <si>
+    <t>£33.97</t>
+  </si>
+  <si>
+    <t>£33.18</t>
+  </si>
+  <si>
+    <t>£40.21</t>
+  </si>
+  <si>
+    <t>£37.80</t>
+  </si>
+  <si>
+    <t>£39.64</t>
+  </si>
+  <si>
+    <t>Blocked / Price Not Loaded</t>
+  </si>
+  <si>
+    <t>£10.57</t>
+  </si>
+  <si>
+    <t>£12.09</t>
+  </si>
+  <si>
+    <t>£15.27</t>
+  </si>
+  <si>
+    <t>£15.86</t>
+  </si>
+  <si>
+    <t>£19.78</t>
+  </si>
+  <si>
+    <t>£22.06</t>
+  </si>
+  <si>
+    <t>£22.13</t>
+  </si>
+  <si>
+    <t>£25.48</t>
+  </si>
+  <si>
+    <t>£33.14</t>
+  </si>
+  <si>
+    <t>£41.19</t>
+  </si>
+  <si>
+    <t>£40.68</t>
+  </si>
+  <si>
+    <t>£11.97</t>
+  </si>
+  <si>
+    <t>£13.99</t>
+  </si>
+  <si>
+    <t>£16.97</t>
+  </si>
+  <si>
+    <t>£19.53</t>
+  </si>
+  <si>
+    <t>£23.24</t>
+  </si>
+  <si>
+    <t>£25.62</t>
+  </si>
+  <si>
+    <t>£28.06</t>
+  </si>
+  <si>
+    <t>£31.30</t>
+  </si>
+  <si>
+    <t>£32.79</t>
+  </si>
+  <si>
+    <t>£37.65</t>
+  </si>
+  <si>
+    <t>£38.85</t>
+  </si>
+  <si>
+    <t>£44.00</t>
+  </si>
+  <si>
+    <t>£51.74</t>
+  </si>
+  <si>
+    <t>£48.20</t>
+  </si>
+  <si>
+    <t>£9.77</t>
+  </si>
+  <si>
+    <t>£11.89</t>
+  </si>
+  <si>
+    <t>£14.31</t>
+  </si>
+  <si>
+    <t>£15.37</t>
+  </si>
+  <si>
+    <t>£19.17</t>
+  </si>
+  <si>
+    <t>£21.62</t>
+  </si>
+  <si>
+    <t>£21.00</t>
+  </si>
+  <si>
+    <t>£24.45</t>
+  </si>
+  <si>
+    <t>£26.38</t>
+  </si>
+  <si>
+    <t>£26.04</t>
+  </si>
+  <si>
+    <t>£32.91</t>
+  </si>
+  <si>
+    <t>£37.42</t>
+  </si>
+  <si>
+    <t>£40.35</t>
+  </si>
+  <si>
+    <t>£39.60</t>
+  </si>
+  <si>
+    <t>£15.09</t>
+  </si>
+  <si>
+    <t>£17.57</t>
+  </si>
+  <si>
+    <t>£20.52</t>
+  </si>
+  <si>
+    <t>£21.94</t>
+  </si>
+  <si>
+    <t>£26.69</t>
+  </si>
+  <si>
+    <t>£31.53</t>
+  </si>
+  <si>
+    <t>£31.37</t>
+  </si>
+  <si>
+    <t>£34.71</t>
+  </si>
+  <si>
+    <t>£37.96</t>
+  </si>
+  <si>
+    <t>£46.12</t>
+  </si>
+  <si>
+    <t>£44.15</t>
+  </si>
+  <si>
+    <t>£53.47</t>
+  </si>
+  <si>
+    <t>£54.40</t>
+  </si>
+  <si>
+    <t>£67.76</t>
+  </si>
+  <si>
     <t>Price Not Found</t>
-  </si>
-  <si>
-    <t>£22.16</t>
-  </si>
-  <si>
-    <t>£47.08</t>
-  </si>
-  <si>
-    <t>£41.25</t>
-  </si>
-  <si>
-    <t>£27.49</t>
-  </si>
-  <si>
-    <t>£14.38</t>
-  </si>
-  <si>
-    <t>£16.01</t>
-  </si>
-  <si>
-    <t>£10.15</t>
-  </si>
-  <si>
-    <t>£12.47</t>
-  </si>
-  <si>
-    <t>£14.62</t>
-  </si>
-  <si>
-    <t>£15.68</t>
-  </si>
-  <si>
-    <t>£19.71</t>
-  </si>
-  <si>
-    <t>£22.56</t>
-  </si>
-  <si>
-    <t>£23.59</t>
-  </si>
-  <si>
-    <t>£27.44</t>
-  </si>
-  <si>
-    <t>£27.15</t>
-  </si>
-  <si>
-    <t>£33.97</t>
-  </si>
-  <si>
-    <t>£33.18</t>
-  </si>
-  <si>
-    <t>£40.21</t>
-  </si>
-  <si>
-    <t>£37.80</t>
-  </si>
-  <si>
-    <t>£39.64</t>
-  </si>
-  <si>
-    <t>Error: 'NoneType' object has no attribute 'find_all'</t>
-  </si>
-  <si>
-    <t>£10.57</t>
-  </si>
-  <si>
-    <t>£12.09</t>
-  </si>
-  <si>
-    <t>£15.27</t>
-  </si>
-  <si>
-    <t>£15.86</t>
-  </si>
-  <si>
-    <t>£19.78</t>
-  </si>
-  <si>
-    <t>£22.06</t>
-  </si>
-  <si>
-    <t>£22.13</t>
-  </si>
-  <si>
-    <t>£25.48</t>
-  </si>
-  <si>
-    <t>£33.14</t>
-  </si>
-  <si>
-    <t>£41.19</t>
-  </si>
-  <si>
-    <t>£40.68</t>
-  </si>
-  <si>
-    <t>£11.97</t>
-  </si>
-  <si>
-    <t>£13.99</t>
-  </si>
-  <si>
-    <t>£16.97</t>
-  </si>
-  <si>
-    <t>£19.53</t>
-  </si>
-  <si>
-    <t>£23.24</t>
-  </si>
-  <si>
-    <t>£25.62</t>
-  </si>
-  <si>
-    <t>£28.06</t>
-  </si>
-  <si>
-    <t>£31.30</t>
-  </si>
-  <si>
-    <t>£32.79</t>
-  </si>
-  <si>
-    <t>£37.65</t>
-  </si>
-  <si>
-    <t>£38.85</t>
-  </si>
-  <si>
-    <t>£44.00</t>
-  </si>
-  <si>
-    <t>£51.74</t>
-  </si>
-  <si>
-    <t>£48.20</t>
-  </si>
-  <si>
-    <t>£9.77</t>
-  </si>
-  <si>
-    <t>£11.89</t>
-  </si>
-  <si>
-    <t>£14.31</t>
-  </si>
-  <si>
-    <t>£15.37</t>
-  </si>
-  <si>
-    <t>£19.17</t>
-  </si>
-  <si>
-    <t>£21.62</t>
-  </si>
-  <si>
-    <t>£21.00</t>
-  </si>
-  <si>
-    <t>£24.45</t>
-  </si>
-  <si>
-    <t>£26.38</t>
-  </si>
-  <si>
-    <t>£26.04</t>
-  </si>
-  <si>
-    <t>£32.91</t>
-  </si>
-  <si>
-    <t>£37.42</t>
-  </si>
-  <si>
-    <t>£40.35</t>
-  </si>
-  <si>
-    <t>£39.60</t>
-  </si>
-  <si>
-    <t>£15.09</t>
-  </si>
-  <si>
-    <t>£17.57</t>
-  </si>
-  <si>
-    <t>£20.52</t>
-  </si>
-  <si>
-    <t>£21.94</t>
-  </si>
-  <si>
-    <t>£26.69</t>
-  </si>
-  <si>
-    <t>£31.53</t>
-  </si>
-  <si>
-    <t>£31.37</t>
-  </si>
-  <si>
-    <t>£34.71</t>
-  </si>
-  <si>
-    <t>£37.96</t>
-  </si>
-  <si>
-    <t>£46.12</t>
-  </si>
-  <si>
-    <t>£44.15</t>
-  </si>
-  <si>
-    <t>£53.47</t>
-  </si>
-  <si>
-    <t>£54.40</t>
-  </si>
-  <si>
-    <t>£67.76</t>
   </si>
 </sst>
 </file>
@@ -930,7 +933,7 @@
         <v>57</v>
       </c>
       <c r="Q2" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -983,7 +986,7 @@
         <v>57</v>
       </c>
       <c r="Q3" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -1036,7 +1039,7 @@
         <v>57</v>
       </c>
       <c r="Q4" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -1089,7 +1092,7 @@
         <v>57</v>
       </c>
       <c r="Q5" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -1142,7 +1145,7 @@
         <v>57</v>
       </c>
       <c r="Q6" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -1195,7 +1198,7 @@
         <v>57</v>
       </c>
       <c r="Q7" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -1248,7 +1251,7 @@
         <v>57</v>
       </c>
       <c r="Q8" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -1301,7 +1304,7 @@
         <v>57</v>
       </c>
       <c r="Q9" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -1354,7 +1357,7 @@
         <v>57</v>
       </c>
       <c r="Q10" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1407,7 +1410,7 @@
         <v>57</v>
       </c>
       <c r="Q11" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1513,7 +1516,7 @@
         <v>57</v>
       </c>
       <c r="Q13" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1672,7 +1675,7 @@
         <v>57</v>
       </c>
       <c r="Q16" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
